--- a/artfynd/A 34503-2022 artfynd.xlsx
+++ b/artfynd/A 34503-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118703379</v>
+        <v>118700512</v>
       </c>
       <c r="B2" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482580</v>
+        <v>482106</v>
       </c>
       <c r="R2" t="n">
-        <v>6853555</v>
+        <v>6853766</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118700512</v>
+        <v>118703379</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482106</v>
+        <v>482580</v>
       </c>
       <c r="R3" t="n">
-        <v>6853766</v>
+        <v>6853555</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 34503-2022 artfynd.xlsx
+++ b/artfynd/A 34503-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118700512</v>
+        <v>118703379</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482106</v>
+        <v>482580</v>
       </c>
       <c r="R2" t="n">
-        <v>6853766</v>
+        <v>6853555</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118703379</v>
+        <v>118700512</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482580</v>
+        <v>482106</v>
       </c>
       <c r="R3" t="n">
-        <v>6853555</v>
+        <v>6853766</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 34503-2022 artfynd.xlsx
+++ b/artfynd/A 34503-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118703379</v>
+        <v>118700512</v>
       </c>
       <c r="B2" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482580</v>
+        <v>482106</v>
       </c>
       <c r="R2" t="n">
-        <v>6853555</v>
+        <v>6853766</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118700512</v>
+        <v>118703379</v>
       </c>
       <c r="B3" t="n">
-        <v>79572</v>
+        <v>79573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482106</v>
+        <v>482580</v>
       </c>
       <c r="R3" t="n">
-        <v>6853766</v>
+        <v>6853555</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
